--- a/webapp/public/templates/13. XLSC MẠNG NGOẠI VI_TUẤN.xlsx
+++ b/webapp/public/templates/13. XLSC MẠNG NGOẠI VI_TUẤN.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B30_TUAN" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,58 +413,72 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Cột 1</t>
+          <t>XLSC MNV - TÂY NINH &amp; LONG AN (01/07/2026 – 01/08/2026)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Cột 2</t>
+          <t>XLSC MNV - TÂY NINH &amp; LONG AN (01/07/2026 – 01/08/2026)</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Cột 3</t>
+          <t>XLSC MNV - TÂY NINH &amp; LONG AN (01/07/2026 – 01/08/2026)</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Cột 4</t>
+          <t>XLSC MNV - TÂY NINH &amp; LONG AN (01/07/2026 – 01/08/2026)</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Cột 5</t>
+          <t>XLSC MNV - TÂY NINH &amp; LONG AN (01/07/2026 – 01/08/2026)</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Cột 6</t>
+          <t>XLSC MNV - TÂY NINH &amp; LONG AN (01/07/2026 – 01/08/2026)</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Cột 7</t>
+          <t>XLSC MNV - TÂY NINH &amp; LONG AN (01/07/2026 – 01/08/2026)</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Cột 8</t>
+          <t>XLSC MNV - TÂY NINH &amp; LONG AN (01/07/2026 – 01/08/2026)</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Cột 9</t>
+          <t>XLSC MNV - TÂY NINH &amp; LONG AN (01/07/2026 – 01/08/2026)</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Cột 10</t>
+          <t>XLSC MNV - TÂY NINH &amp; LONG AN (01/07/2026 – 01/08/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Bến Lức</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Đức Hòa</t>
         </is>
       </c>
     </row>

--- a/webapp/public/templates/13. XLSC MẠNG NGOẠI VI_TUẤN.xlsx
+++ b/webapp/public/templates/13. XLSC MẠNG NGOẠI VI_TUẤN.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,14 +471,208 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bến Lức</t>
+          <t>Khu vực</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Tổng giao</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Hoàn thành</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>HT đúng hạn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>HT quá hạn</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>TL HT đúng hạn</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Tổng tồn</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Tồn trong hạn</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Tồn quá hạn</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>TL tồn QH</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Đức Hòa</t>
+          <t>Tây Ninh</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Long An</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>99.03%</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>99.12%</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
